--- a/public/exercicios/treino-compras-02-procv.xlsx
+++ b/public/exercicios/treino-compras-02-procv.xlsx
@@ -28,13 +28,13 @@
     <t>Excel PT-BR: =PROCV(A2;Base!A:D;4;FALSO)</t>
   </si>
   <si>
-    <t>Excel EN / Sheets: =VLOOKUP(A2,Base!A:D,4,FALSE)</t>
+    <t>Excel EN: =VLOOKUP(A2,Base!A:D,4,FALSE)</t>
   </si>
   <si>
     <t>Arraste até a última linha.</t>
   </si>
   <si>
-    <t>Salve .xlsx e envie no site.</t>
+    <t>Se estiver só visualizando: Editar no navegador / Salvar uma cópia.</t>
   </si>
   <si>
     <t>Codigo</t>
